--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.khalilov\Desktop\tuski_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70D9715-7277-47FC-9A2C-D8F93F1379BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96010F39-D83C-4715-8851-0C06751E27B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="117">
   <si>
     <t>perfume</t>
   </si>
@@ -610,6 +610,226 @@
   </si>
   <si>
     <t>BURROCACAO</t>
+  </si>
+  <si>
+    <t>BIG Professional</t>
+  </si>
+  <si>
+    <r>
+      <t>ფრჩხილის ლაქი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> პროფესიონალური ხარისხის ლაქი იდეალური დაფარვისა და მდგრადობისთვის.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dırnaq boyası
+Mükəmməl örtücülük və uzunmüddətli qalıcılıq üçün peşəkar keyfiyyətli dırnaq boyası.</t>
+  </si>
+  <si>
+    <r>
+      <t>Лак для ногтей</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Профессиональное качество для идеального покрытия и стойкости.</t>
+    </r>
+  </si>
+  <si>
+    <t>BIG PROFESSIONAL</t>
+  </si>
+  <si>
+    <t>BIG PROFESSIONAL-ის ბრენდის, "exclusive" სერიის ასაძრობი (removable) ფრჩხილის ლაქი.</t>
+  </si>
+  <si>
+    <t>Exclusive Removable Nail Polish
+Yüksək keyfiyyətli, asanlıqla çıxarıla bilən (removable) eksklüziv dırnaq boyası</t>
+  </si>
+  <si>
+    <t>Exclusive Removable Nail Polish
+Эксклюзивный съемный (removable) лак для ногтей профессионального качества.</t>
+  </si>
+  <si>
+    <t>OXXI Professiona</t>
+  </si>
+  <si>
+    <t>პროფესიონალური ზედაპირული დამფარავი (ტოპი) წებოვანი ფენის გარეშე</t>
+  </si>
+  <si>
+    <t>Yapışqan qatı olmayan peşəkar üst örtük (top).</t>
+  </si>
+  <si>
+    <t>Профессиональное верхнее покрытие (топ) без липкого слоя</t>
+  </si>
+  <si>
+    <t>KLIO Professional</t>
+  </si>
+  <si>
+    <r>
+      <t>Brilliant Top Coat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> უმაღლესი ხარისხის ზედაპირული დამფარავი (ტოპი) განსაკუთრებული ბზინვარებისთვის.</t>
+    </r>
+  </si>
+  <si>
+    <t>Brilliant Top Coat
+Xüsusi parlaqlıq üçün yüksək keyfiyyətli üst örtük (top).</t>
+  </si>
+  <si>
+    <r>
+      <t>Brilliant Top Coat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Высококачественное верхнее покрытие (топ) для невероятного блеска.</t>
+    </r>
+  </si>
+  <si>
+    <t>OXXI Professional</t>
+  </si>
+  <si>
+    <t>პროფესიონალური კაუჩუკის ბაზა ფრჩხილის ზედაპირის სრულყოფილი გასწორებისთვის.</t>
+  </si>
+  <si>
+    <t>Dırnaq səthinin mükəmməl hamarlanması üçün peşəkar kauçuk baza.</t>
+  </si>
+  <si>
+    <t>Профессиональная каучуковая база для идеального выравнивания ногтевой пластины.</t>
+  </si>
+  <si>
+    <r>
+      <t>მინისებრი ტოპი (Стеклянный Тор)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> პროფესიონალური ზედაპირული დამფარავი განსაკუთრებული, სარკისებრი ბზინვარებისთვის.</t>
+    </r>
+  </si>
+  <si>
+    <t>Şüşə effektli top (Стеклянный Тор)
+Xüsusi güzgü parıltısı üçün peşəkar üst örtük (top).</t>
+  </si>
+  <si>
+    <r>
+      <t>Стеклянный Тор</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Профессиональное верхнее покрытие для создания исключительного зеркального блеска.</t>
+    </r>
+  </si>
+  <si>
+    <t>Messier Professional</t>
+  </si>
+  <si>
+    <r>
+      <t>აკრილისა და გელ-ლაქის მოსაცილებელი სითხე</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> პროფესიონალური საშუალება ფრჩხილის საფარის სწრაფი და უსაფრთხო მოცილებისთვის.</t>
+    </r>
+  </si>
+  <si>
+    <t>Akril və gel təmizləyici maye
+Dırnaq örtüyünün sürətli və təhlükəsiz çıxarılması üçün peşəkar vasitə.</t>
+  </si>
+  <si>
+    <r>
+      <t>Жидкость для снятия акрила и гель-лака</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Профессиональное средство для быстрого и безопасного снятия ногтевого покрытия.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kodi Professional</t>
+  </si>
+  <si>
+    <r>
+      <t>Cuticle Remover</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> პროფესიონალური საშუალება კუტიკულის სწრაფი და ეფექტური დარბილებისა და მოცილებისთვის.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cuticle Remover
+Kutikulanın (dırnaq ətrafı dərinin) sürətli və effektiv yumşaldılması və təmizlənməsi üçün peşəkar vasitə.</t>
+  </si>
+  <si>
+    <r>
+      <t>Cuticle Remover</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Профессиональное средство для быстрого и эффективного размягчения и удаления кутикулы.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -712,14 +932,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -1004,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1172,7 +1392,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7">
+      <c r="A7" s="3">
         <v>10101</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1181,7 +1401,7 @@
       <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>10</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -1190,7 +1410,7 @@
       <c r="F7" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H7" t="s">
@@ -1198,7 +1418,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="7">
+      <c r="A8" s="3">
         <v>10102</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1207,7 +1427,7 @@
       <c r="C8" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="3">
         <v>6</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -1216,7 +1436,7 @@
       <c r="F8" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>32</v>
       </c>
       <c r="H8" t="s">
@@ -1224,7 +1444,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7">
+      <c r="A9" s="3">
         <v>10103</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1233,7 +1453,7 @@
       <c r="C9" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="3">
         <v>6</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -1242,7 +1462,7 @@
       <c r="F9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>37</v>
       </c>
       <c r="H9" t="s">
@@ -1250,7 +1470,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7">
+      <c r="A10" s="3">
         <v>10104</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1259,7 +1479,7 @@
       <c r="C10" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="3">
         <v>6</v>
       </c>
       <c r="E10" s="6" t="s">
@@ -1268,7 +1488,7 @@
       <c r="F10" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>41</v>
       </c>
       <c r="H10" t="s">
@@ -1276,7 +1496,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="7">
+      <c r="A11" s="3">
         <v>10105</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1285,7 +1505,7 @@
       <c r="C11" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="3">
         <v>12</v>
       </c>
       <c r="E11" s="6" t="s">
@@ -1302,7 +1522,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="7">
+      <c r="A12" s="3">
         <v>10106</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1311,7 +1531,7 @@
       <c r="C12" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="3">
         <v>12</v>
       </c>
       <c r="E12" s="6" t="s">
@@ -1328,7 +1548,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="7">
+      <c r="A13" s="3">
         <v>10107</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1337,7 +1557,7 @@
       <c r="C13" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="3">
         <v>7</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -1354,7 +1574,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="7">
+      <c r="A14" s="3">
         <v>10108</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1363,7 +1583,7 @@
       <c r="C14" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="3">
         <v>12</v>
       </c>
       <c r="E14" s="6" t="s">
@@ -1380,7 +1600,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7">
+      <c r="A15" s="3">
         <v>10109</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1389,7 +1609,7 @@
       <c r="C15" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="3">
         <v>6</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -1406,7 +1626,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="7">
+      <c r="A16" s="3">
         <v>10110</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -1415,7 +1635,7 @@
       <c r="C16" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="3">
         <v>6</v>
       </c>
       <c r="E16" s="6" t="s">
@@ -1432,7 +1652,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7">
+      <c r="A17" s="3">
         <v>10111</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1441,7 +1661,7 @@
       <c r="C17" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="3">
         <v>6</v>
       </c>
       <c r="E17" s="6" t="s">
@@ -1458,7 +1678,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="7">
+      <c r="A18" s="3">
         <v>10112</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1467,7 +1687,7 @@
       <c r="C18" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="3">
         <v>12</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -1476,7 +1696,7 @@
       <c r="F18" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="8" t="s">
         <v>72</v>
       </c>
       <c r="H18" s="4" t="s">
@@ -1484,7 +1704,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="7">
+      <c r="A19" s="3">
         <v>10113</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1493,7 +1713,7 @@
       <c r="C19" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="3">
         <v>8</v>
       </c>
       <c r="E19" s="6" t="s">
@@ -1502,7 +1722,7 @@
       <c r="F19" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="8" t="s">
         <v>75</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -1510,7 +1730,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="7">
+      <c r="A20" s="3">
         <v>10114</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1519,7 +1739,7 @@
       <c r="C20" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="6">
         <v>6</v>
       </c>
       <c r="E20" s="6" t="s">
@@ -1528,11 +1748,216 @@
       <c r="F20" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="8" t="s">
         <v>79</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="9">
+        <v>10115</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="10">
+        <v>8</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="9">
+        <v>10116</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="10">
+        <v>8</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="9">
+        <v>10117</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="10">
+        <v>10</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="9">
+        <v>10118</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="10">
+        <v>7</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="9">
+        <v>10119</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" s="10">
+        <v>10</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="9">
+        <v>10120</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="10">
+        <v>7</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="9">
+        <v>10121</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="10">
+        <v>8</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="9">
+        <v>10122</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.khalilov\Desktop\tuski_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96010F39-D83C-4715-8851-0C06751E27B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7DDFE6-0B0A-49A2-A555-FCEA950E106C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1947,6 +1947,9 @@
       <c r="C28" s="4" t="s">
         <v>113</v>
       </c>
+      <c r="D28" s="10">
+        <v>9</v>
+      </c>
       <c r="E28" s="6" t="s">
         <v>21</v>
       </c>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.khalilov\Desktop\tuski_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7DDFE6-0B0A-49A2-A555-FCEA950E106C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEF8A65-B730-4E34-835D-A6B97C9310D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
   <si>
     <t>perfume</t>
   </si>
@@ -33,12 +33,6 @@
     <t>მდგრადი არომატი...</t>
   </si>
   <si>
-    <t>Vanil və müşk...</t>
-  </si>
-  <si>
-    <t>Long-lasting...</t>
-  </si>
-  <si>
     <t>salon</t>
   </si>
   <si>
@@ -57,12 +51,6 @@
     <t>lipstick</t>
   </si>
   <si>
-    <t>Mat dodaq boyası</t>
-  </si>
-  <si>
-    <t>Matte lipstick...</t>
-  </si>
-  <si>
     <t>Rubber Base Global Fashion</t>
   </si>
   <si>
@@ -106,9 +94,6 @@
   </si>
   <si>
     <t>Is_Pro</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Description_RU</t>
   </si>
   <si>
     <t>NO</t>
@@ -830,6 +815,27 @@
       </rPr>
       <t xml:space="preserve"> Профессиональное средство для быстрого и эффективного размягчения и удаления кутикулы.</t>
     </r>
+  </si>
+  <si>
+    <t>Description_RU</t>
+  </si>
+  <si>
+    <t>Dodaq yumşaldıcı</t>
+  </si>
+  <si>
+    <t>Смягчающее средство для губ</t>
+  </si>
+  <si>
+    <t>Gigiyenik dodaq boyası</t>
+  </si>
+  <si>
+    <t>Гигиеническая помада</t>
+  </si>
+  <si>
+    <t>Qalıcı ətir</t>
+  </si>
+  <si>
+    <t>Стойкий аромат</t>
   </si>
 </sst>
 </file>
@@ -914,7 +920,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -937,12 +943,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1239,28 +1239,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
-        <v>23</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1271,22 +1271,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D2" s="2">
         <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>3</v>
+      <c r="G2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1294,25 +1294,25 @@
         <v>555001</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D3" s="2">
         <v>11.5</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>11</v>
+        <v>77</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1320,49 +1320,51 @@
         <v>555002</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D4" s="2">
         <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1"/>
+        <v>79</v>
+      </c>
+      <c r="G4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>999888</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2">
         <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1370,25 +1372,25 @@
         <v>11111</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3">
         <v>6</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1396,25 +1398,25 @@
         <v>10101</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3">
         <v>10</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1422,25 +1424,25 @@
         <v>10102</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3">
         <v>6</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1448,25 +1450,25 @@
         <v>10103</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3">
         <v>6</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1474,25 +1476,25 @@
         <v>10104</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D10" s="3">
         <v>6</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1500,25 +1502,25 @@
         <v>10105</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D11" s="3">
         <v>12</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1526,25 +1528,25 @@
         <v>10106</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D12" s="3">
         <v>12</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1552,25 +1554,25 @@
         <v>10107</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D13" s="3">
         <v>7</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1578,25 +1580,25 @@
         <v>10108</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D14" s="3">
         <v>12</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1604,25 +1606,25 @@
         <v>10109</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D15" s="3">
         <v>6</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1630,25 +1632,25 @@
         <v>10110</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D16" s="3">
         <v>6</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1656,25 +1658,25 @@
         <v>10111</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D17" s="3">
         <v>6</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1682,25 +1684,25 @@
         <v>10112</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D18" s="3">
         <v>12</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1708,25 +1710,25 @@
         <v>10113</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D19" s="3">
         <v>8</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -1734,233 +1736,233 @@
         <v>10114</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D20" s="6">
         <v>6</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="9">
+      <c r="A21" s="3">
         <v>10115</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" s="6">
+        <v>8</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3">
+        <v>10116</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="6">
+        <v>8</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="10">
+      <c r="G22" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3">
+        <v>10117</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="6">
+        <v>10</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" t="s">
+        <v>90</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3">
+        <v>10118</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D24" s="6">
+        <v>7</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3">
+        <v>10119</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="6">
+        <v>10</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" t="s">
+        <v>98</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="3">
+        <v>10120</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="6">
+        <v>7</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="3">
+        <v>10121</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D27" s="6">
         <v>8</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="9">
-        <v>10116</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="10">
-        <v>8</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="9">
-        <v>10117</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" s="10">
-        <v>10</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" t="s">
-        <v>95</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="H23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="9">
-        <v>10118</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="10">
-        <v>7</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="9">
-        <v>10119</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" t="s">
-        <v>102</v>
-      </c>
-      <c r="D25" s="10">
-        <v>10</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F25" t="s">
-        <v>103</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="H25" t="s">
+      <c r="E27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="9">
-        <v>10120</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" s="10">
-        <v>7</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" s="4" t="s">
+      <c r="G27" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="H27" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H26" s="4" t="s">
+    </row>
+    <row r="28" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="3">
+        <v>10122</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="9">
-        <v>10121</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="D28" s="6">
+        <v>9</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="10">
-        <v>8</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="4" t="s">
+      <c r="G28" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="H28" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="9">
-        <v>10122</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28" s="10">
-        <v>9</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.khalilov\Desktop\tuski_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEF8A65-B730-4E34-835D-A6B97C9310D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3D72D5-7535-4939-A8D1-31C6346AB096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="180">
   <si>
     <t>perfume</t>
   </si>
@@ -836,6 +847,488 @@
   </si>
   <si>
     <t>Стойкий аромат</t>
+  </si>
+  <si>
+    <t>SHANILAK Professional</t>
+  </si>
+  <si>
+    <r>
+      <t>მოცვის არომატი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> პროფესიონალური ხაზის მოვლის საშუალება, რომელიც გამდიდრებულია ნატურალური ექსტრაქტებით. მოცვის ფორმულა უზრუნველყოფს ინტენსიურ დატენიანებასა და კვებას. პროდუქტი გამოირჩევა გამაჯანსაღებელი სურნელით და იდეალურია პროფესიონალური შედეგისთვის.</t>
+    </r>
+  </si>
+  <si>
+    <t>Qarağat (Mavi gilas) ətri
+Təbii ekstraktlarla zənginləşdirilmiş peşəkar qulluq vasitəsi. Qarağat tərkibli formula intensiv nəmləndirmə və qidalanmanı təmin edir. Məhsul xoş və təravətləndirici ətri ilə seçilir, gündəlik istifadə və peşəkar nəticə üçün mükəmməldir</t>
+  </si>
+  <si>
+    <r>
+      <t>Черничный микс</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Профессиональное средство для ухода, обогащенное натуральными экстрактами. Формула с черникой обеспечивает интенсивное увлажнение и питание. Продукт обладает освежающим ароматом и идеально подходит для достижения профессионального результата.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Poly Gel (Skin Cover 06)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ინოვაციური აკრილ-გელი, რომელიც აერთიანებს აკრილის სიმტკიცესა და გელის ელასტიურობას. იდეალურია ფრჩხილის დაგრძელებისა და გამაგრებისთვის. Skin Cover 06 ჩრდილი უზრუნველყოფს ბუნებრივ და დახვეწილ დაფარვას. შრება UV/LED ლამპაში.</t>
+    </r>
+  </si>
+  <si>
+    <t>Poly Gel (Skin Cover 06)
+Akrilin davamlılığı ilə gelin elastikliyini birləşdirən innovativ akril-gel. Dırnaqların uzadılması və möhkəmləndirilməsi üçün idealdır. Skin Cover 06 çaları təbii və zərif görünüş bəxş edir. UV/LED lampasında quruyur.</t>
+  </si>
+  <si>
+    <r>
+      <t>Poly Gel (Skin Cover 06)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Инновационный акрил-гель, сочетающий в себе прочность акрила и эластичность геля. Идеально подходит для наращивания и укрепления ногтей. Оттенок Skin Cover 06 обеспечивает естественное и нежное покрытие. Полимеризуется в UV/LED лампах.</t>
+    </r>
+  </si>
+  <si>
+    <t>BiG Professional</t>
+  </si>
+  <si>
+    <r>
+      <t>Gel Polish</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> მაღალი ხარისხის პროფესიონალური გელ-ლაქი. გამოირჩევა პიგმენტაციის მაღალი დონით, თანაბარი დაფარვითა და ხანგრძლივი მდგრადობით. ფორმულა უზრუნველყოფს ფრჩხილის დაცვას და ბრწყინვალე ეფექტს კვირების განმავლობაში.</t>
+    </r>
+  </si>
+  <si>
+    <t>Gel Polish
+Yüksək keyfiyyətli peşəkar gel-lak. Yüksək piqmentasiya, bərabər paylanma və uzunmüddətli davamlılığı ilə seçilir. Formula dırnaqların qorunmasını və həftələrlə davam edən parlaq effekti təmin edir.</t>
+  </si>
+  <si>
+    <r>
+      <t>Gel Polish</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Высококачественный профессиональный гель-лак. Отличается высокой пигментацией, равномерным нанесением и длительной стойкостью. Формула обеспечивает защиту ногтей и блестящий эффект в течение нескольких недель.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>მანიკურის ხის ჩხირები</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ნატურალური ნარინჯისფერი ხისგან დამზადებული ორმხრივი ჩხირები კუტიკულის მოსავლელად. წვეტიანი ბოლო გამოიყენება ფრჩხილის გასასუფთავებლად, ხოლო ბრტყელი — კუტიკულის ნაზად უკან დასახევად. აუცილებელი აქსესუარია ჰიგიენური და პროფესიონალური მანიკურისთვის.</t>
+    </r>
+  </si>
+  <si>
+    <t>Manikür üçün taxta çubuqlar
+Kutikula baxımı üçün təbii portağal ağacından hazırlanmış ikitərəfli çubuqlar. Sivri ucu dırnaqaltı təmizlik, yastı ucu isə kutikulanı zədələmədən geri itələmək üçün nəzərdə tutulub. Gigiyenik və peşəkar manikür üçün əvəzolunmaz vasitədir.</t>
+  </si>
+  <si>
+    <r>
+      <t>Апельсиновые палочки для маникюра</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Двусторонние палочки из натурального апельсинового дерева для ухода за кутикулой. Острый конец используется для очистки ногтей, а скошенный — для мягкого отодвигания кутикулы. Незаменимый аксессуар для гигиеничного и профессионального маникюра.</t>
+    </r>
+  </si>
+  <si>
+    <t>Пилка для ногтей (180/240)</t>
+  </si>
+  <si>
+    <r>
+      <t>ფრჩხილის ქლიბი (180/240)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> მაღალი ხარისხის, ორმხრივი პროფესიონალური ქლიბი "super wearproof" ტექნოლოგიით. 180 გრიტი განკუთვნილია ფრჩხილის ფორმირებისთვის, ხოლო 240 გრიტი — ზედაპირის ნაზი დამუშავებისთვის. გამძლეა და ინარჩუნებს თვისებებს ხანგრძლივი გამოყენებისას.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dırnaq pülüşü (180/240)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "Super wearproof" texnologiyası ilə hazırlanmış yüksək keyfiyyətli peşəkar ikitərəfli dırnaq pülüşü (pilka). 180 qrit dırnağa forma vermək, 240 qrit isə səthi incə cilalamaq üçündür. Uzunmüddətli istifadə üçün davamlıdır.</t>
+    </r>
+  </si>
+  <si>
+    <t>Quru kutikula yağı
+Kutikulanın intensiv nəmləndirilməsi üçün ikifazalı quru yağ. Formula dərhal sorulur, yağlı iz qoymur, dərini yumşaq və baxımlı edir. Manikürün son mərhələsi üçün idealdır</t>
+  </si>
+  <si>
+    <r>
+      <t>масло для кутикулы</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Двухфазное сухое масло для интенсивного увлажнения кутикулы. Формула быстро впитывается, не оставляя жирного блеска, делает кожу мягкой и ухоженной. Идеально подходит для завершения процедуры маникюра.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ზეთი კუტიკულისთვის</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ორფაზიანი მშრალი ზეთი კუტიკულის ინტენსიური დატენიანებისთვის. ფორმულა სწრაფად შეიწოვება, არ ტოვებს ცხიმოვან კვალს და კანს ანიჭებს რბილ და მოვლილ იერს. იდეალურია მანიკურის დასასრულებლად.</t>
+    </r>
+  </si>
+  <si>
+    <t>CRISMO Professional</t>
+  </si>
+  <si>
+    <r>
+      <t>კუტიკულის ზეთი</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> პროფესიონალური ფორმულა კუტიკულის ღრმა კვებისა და აღდგენისთვის. ნატურალური ექსტრაქტებით გამდიდრებული ზეთი არბილებს კანს, ხელს უშლის მის გამოშრობას და ფრჩხილებს ჯანსაღ იერს ანიჭებს. იდეალურია ყოველდღიური მოვლისთვის.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kutikula yağı
+Kutikulanın dərindən qidalanması və bərpası üçün peşəkar formula. Təbii ekstraktlarla zənginləşdirilmiş yağ dərini yumşaldır, qurumasının qarşısını alır və dırnaqlara sağlam görünüş bəxş edir. Gündəlik qulluq üçün idealdır.</t>
+  </si>
+  <si>
+    <r>
+      <t>Масло для кутикулы</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Профессиональная формула для глубокого питания и восстановления кутикулы. Масло, обогащенное натуральными экстрактами, смягчает кожу, предотвращает ее пересыхание и придает ногтям здоровый вид. Идеально подходит для ежедневного ухода.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Builder Gel (N 022)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> პროფესიონალური სამფაზიანი საშენი გელი ფრჩხილის დაგრძელებისა და მოდელირებისთვის. გამოირჩევა თვითსწორებადი ტექსტურით, მაღალი მდგრადობითა და ოპტიმალური სიმკვრივით. იდეალურია ნებისმიერი ფორმის ფრჩხილის შესაქმნელად.</t>
+    </r>
+  </si>
+  <si>
+    <t>Builder Gel (N 022)
+Dırnaqların qaynağı və modelləşdirilməsi üçün peşəkar qurucu (builder) gel. Öz-özünə düzələn teksturaya, yüksək davamlılığa və optimal qatılığa malikdir. İstənilən dırnaq formasını yaratmaq üçün mükəmməldir.</t>
+  </si>
+  <si>
+    <r>
+      <t>Builder Gel (N 022)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Профессиональный конструирующий гель для наращивания и моделирования ногтей. Обладает самовыравнивающейся текстурой, высокой прочностью и оптимальной вязкостью. Идеально подходит для создания любой формы ногтей.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BIG Professional </t>
+  </si>
+  <si>
+    <r>
+      <t>რძისფერი გელი შიმერით</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> პროფესიონალური საშენი გელი ნაზი რძისფერი ტონითა და წვრილი ბრჭყვიალა (შიმერი) ნაწილაკებით. იდეალურია ფრჩხილის გამაგრების, დაგრძელებისა და დახვეწილი დიზაინის შესაქმნელად. აქვს თვითსწორებადი ფორმულა და ანიჭებს ფრჩხილებს ელეგანტურ ბზინვარებას.</t>
+    </r>
+  </si>
+  <si>
+    <t>Şimmerli südlü gel
+Zərif südlü tonu və incə parıltılı (şimmer) hissəcikləri olan peşəkar qurucu gel. Dırnaqların bərkidilməsi, uzadılması və zərif dizaynların yaradılması üçün idealdır. Öz-özünə düzələn formula malikdir və dırnaqlara eleqant parıltı bəxş edir.</t>
+  </si>
+  <si>
+    <r>
+      <t>Молочный гель с шиммером</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Профессиональный конструирующий гель нежного молочного оттенка с мелкими мерцающими частицами (шиммером). Идеально подходит для укрепления, наращивания и создания утонченного дизайна. Обладает самовыравнивающейся формулой и придает ногтям элегантный блеск.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>გამჭვირვალე საშენი გელი (Clear)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> პროფესიონალური კონსტრუქციული გელი ფრჩხილის დაგრძელებისა და მოდელირებისთვის. გამოირჩევა კრისტალური გამჭვირვალობით, არ ყვითლდება და აქვს შესანიშნავი თვითსწორებადი თვისება. უზრუნველყოფს მაქსიმალურ მდგრადობას.</t>
+    </r>
+  </si>
+  <si>
+    <t>Şəffaf qurucu gel (Clear)
+Dırnaqların qaynağı və modelləşdirilməsi üçün peşəkar konstruksiya geli. Kristal şəffaflığı ilə seçilir, saralmır və mükəmməl öz-özünə düzəlmə qabiliyyətinə malikdir. Maksimum davamlılığı təmin edir.</t>
+  </si>
+  <si>
+    <r>
+      <t>Прозрачный конструирующий гель (Clear)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Профессиональный конструктурирующий гель для наращивания и моделирования ногтей. Отличается кристальной прозрачностью, не желтеет и обладает отличными самовыравнивающимися свойствами. Обеспечивает максимальную прочность.</t>
+    </r>
+  </si>
+  <si>
+    <t>მაგიდის სანათი (Clamp Lamp)</t>
+  </si>
+  <si>
+    <t>Masaüstü çıraq (Masa lambası)</t>
+  </si>
+  <si>
+    <t>Настольная лампа (на струбцине)</t>
+  </si>
+  <si>
+    <t>Double Thick</t>
+  </si>
+  <si>
+    <t>ფრჩხილის დაგრძელების ოქროსფერი ფორმები "Double Thick"</t>
+  </si>
+  <si>
+    <t>Double Thick" Qızılı Rəngli Dırnaq Qaynağı Formaları</t>
+  </si>
+  <si>
+    <t>Золотые формы для наращивания ногтей "Double Thick"</t>
+  </si>
+  <si>
+    <t>"პეპელა"</t>
+  </si>
+  <si>
+    <t>ფრჩხილის დაგრძელების ფერადი ფორმები "პეპელა"</t>
+  </si>
+  <si>
+    <t>"Kəpənək" modelli rəngli dırnaq formaları</t>
+  </si>
+  <si>
+    <t>Цветные формы для наращивания ногтей "Бабочка"</t>
+  </si>
+  <si>
+    <t>Shanilak Professional</t>
+  </si>
+  <si>
+    <r>
+      <t>უსაბუსუსო ხელსახოცები Shanilak Professional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> პროფესიონალური ხელსახოცები მანიკურის, პედიკურისა და კოსმეტიკური პროცედურებისთვის. დამზადებულია მჭიდრო, ელასტიური ბოჭკოსგან</t>
+    </r>
+  </si>
+  <si>
+    <t>Shanilak Professional tüksüz salfetləri
+Manikür, pedikür və kosmetik prosedurlar üçün professional salfetlər. Sıx və elastik lifdən hazırlanmışdır.</t>
+  </si>
+  <si>
+    <r>
+      <t>Безворсовые салфетки Shanilak Professional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Профессиональные салфетки для маникюра, педикюра и косметических процедур. Изготовлены из плотного эластичного волокна.</t>
+    </r>
+  </si>
+  <si>
+    <t>მინი-ბაფების ნაკრები ფრჩხილისთვის</t>
+  </si>
+  <si>
+    <t>მინი-ბაფების</t>
+  </si>
+  <si>
+    <t>Dırnaq üçün mini-baf dəsti</t>
+  </si>
+  <si>
+    <t>Набор мини-бафов для ногтей</t>
+  </si>
+  <si>
+    <t>LED/UV ლამპა</t>
+  </si>
+  <si>
+    <r>
+      <t>პროფესიონალური LED/UV ლამპა ფრჩხილისთვის</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> მძლავრი და კომპაქტური ლამპა ყველა ტიპის გელ-ლაქის სწრაფი და ეფექტური პოლიმერიზაციისთვის.</t>
+    </r>
+  </si>
+  <si>
+    <t>Professional LED/UV dırnaq lampası
+Bütün növ gel-lakların sürətli və effektiv qurudulması üçün güclü və kompakt lampa.</t>
+  </si>
+  <si>
+    <r>
+      <t>Профессиональная LED/UV лампа для ногтей</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Мощная и компактная лампа для быстрой и качественной полимеризации всех видов гель-лаков.</t>
+    </r>
+  </si>
+  <si>
+    <t>ხელსაწყოების სტერილიზაციის კონტეინერი</t>
+  </si>
+  <si>
+    <t>პროფესიონალური სტერილიზაციის ლანგარი მანიკურის, პედიკურის და სილამაზის ინსტრუმენტების დეზინფექციისთვის. აღჭურვილია მოსახსნელი ცხაურით, რაც უზრუნველყოფს ჰიგიენურ და უსაფრთხო მუშაობას ხსნარებთან.</t>
+  </si>
+  <si>
+    <t>Профессиональный лоток для дезинфекции инструментов для маникюра, педикюра и парикмахерских принадлежностей. Оснащен съемным решетчатым поддоном, что обеспечивает безопасный контакт с растворами и удобство в работе.</t>
+  </si>
+  <si>
+    <t>Manikür, pedikür və bərbər alətlərinin dezinfeksiyası üçün nəzərdə tutulmuş peşəkar sterilizasiya qabı. Məhlulla birbaşa təmasdan qaçmaq və təhlükəsizliyi təmin etmək üçün çıxarıla bilən daxili səbətlə təchiz olunmuşdur.</t>
   </si>
 </sst>
 </file>
@@ -1224,15 +1717,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="3" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="40.44140625" customWidth="1"/>
     <col min="4" max="4" width="6.5546875" customWidth="1"/>
     <col min="5" max="5" width="6.77734375" customWidth="1"/>
-    <col min="6" max="6" width="42.33203125" customWidth="1"/>
+    <col min="6" max="6" width="53.6640625" customWidth="1"/>
     <col min="7" max="7" width="47.109375" customWidth="1"/>
     <col min="8" max="9" width="27.44140625" customWidth="1"/>
   </cols>
@@ -1965,7 +2458,486 @@
         <v>111</v>
       </c>
     </row>
+    <row r="29" spans="1:8" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="3">
+        <v>10123</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="6">
+        <v>31</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="3">
+        <v>10124</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" s="6">
+        <v>15</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="3">
+        <v>10125</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" s="6">
+        <v>7</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="3">
+        <v>10126</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="6">
+        <v>4</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="3">
+        <v>10127</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="H33" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="3">
+        <v>10128</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="3">
+        <v>10129</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" t="s">
+        <v>119</v>
+      </c>
+      <c r="D35" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="17.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="3">
+        <v>10130</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
+        <v>139</v>
+      </c>
+      <c r="D36" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="3">
+        <v>10131</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" s="6">
+        <v>9</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="16.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="3">
+        <v>10132</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D38" s="6">
+        <v>10</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="3">
+        <v>10133</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="6">
+        <v>25</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="3">
+        <v>10134</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" t="s">
+        <v>153</v>
+      </c>
+      <c r="D40">
+        <v>30</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" t="s">
+        <v>153</v>
+      </c>
+      <c r="G40" t="s">
+        <v>154</v>
+      </c>
+      <c r="H40" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="3">
+        <v>10135</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>156</v>
+      </c>
+      <c r="D41" s="6">
+        <v>12</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H41" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="3">
+        <v>10136</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" s="6">
+        <v>18</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F42" t="s">
+        <v>161</v>
+      </c>
+      <c r="G42" t="s">
+        <v>162</v>
+      </c>
+      <c r="H42" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="3">
+        <v>10137</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" t="s">
+        <v>164</v>
+      </c>
+      <c r="D43" s="6">
+        <v>5</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="3">
+        <v>10138</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" t="s">
+        <v>169</v>
+      </c>
+      <c r="D44" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" t="s">
+        <v>168</v>
+      </c>
+      <c r="G44" t="s">
+        <v>170</v>
+      </c>
+      <c r="H44" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="3">
+        <v>10139</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="6">
+        <v>35</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="3">
+        <v>10140</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" t="s">
+        <v>177</v>
+      </c>
+      <c r="G46" t="s">
+        <v>179</v>
+      </c>
+      <c r="H46" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="3"/>
+      <c r="B47" s="1"/>
+      <c r="E47" s="6"/>
+    </row>
+    <row r="48" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="3"/>
+      <c r="B48" s="1"/>
+      <c r="E48" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.khalilov\Desktop\tuski_site\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3D72D5-7535-4939-A8D1-31C6346AB096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8722FB-C867-4239-9FE3-685C399F6837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="266">
   <si>
     <t>perfume</t>
   </si>
@@ -1329,6 +1329,264 @@
   </si>
   <si>
     <t>Manikür, pedikür və bərbər alətlərinin dezinfeksiyası üçün nəzərdə tutulmuş peşəkar sterilizasiya qabı. Məhlulla birbaşa təmasdan qaçmaq və təhlükəsizliyi təmin etmək üçün çıxarıla bilən daxili səbətlə təchiz olunmuşdur.</t>
+  </si>
+  <si>
+    <t>Eye Solution</t>
+  </si>
+  <si>
+    <t>თვალის მოვლისა და გასუფთავების სითხე (200 მლ)</t>
+  </si>
+  <si>
+    <t>Göz ətrafı təmizləyici və qulluq mayesi (200 ml)</t>
+  </si>
+  <si>
+    <t>Раствор для ухода и очищения области вокруг глаз (200 мл)</t>
+  </si>
+  <si>
+    <t>(Neckpaper)</t>
+  </si>
+  <si>
+    <t>პროფესიონალური ელასტიური საყელო</t>
+  </si>
+  <si>
+    <t>Peşəkar Elastik Boyun Kağızı</t>
+  </si>
+  <si>
+    <t>Профессиональный эластичный воротничок</t>
+  </si>
+  <si>
+    <t>Cleaning Mousse</t>
+  </si>
+  <si>
+    <t>წამწამების გამწმენდი მუსი</t>
+  </si>
+  <si>
+    <t>Kirpik Təmizləyici Köpük</t>
+  </si>
+  <si>
+    <t>Очищающая мусс-пенка для ресниц</t>
+  </si>
+  <si>
+    <t>Eyelash Remover Brush</t>
+  </si>
+  <si>
+    <t>წამწამების მოსაცილებელი ფუნჯი</t>
+  </si>
+  <si>
+    <t>Kirpik Çıxarıcı Fırça</t>
+  </si>
+  <si>
+    <t>Кисть для снятия ресниц</t>
+  </si>
+  <si>
+    <t>AQUADEX</t>
+  </si>
+  <si>
+    <t>მაღალი დონის სადეზინფექციო საშუალება</t>
+  </si>
+  <si>
+    <t>Yüksək Səviyyəli Dezinfeksiyaedici Vasitə</t>
+  </si>
+  <si>
+    <t>Дезинфицирующее средство высокого уровня</t>
+  </si>
+  <si>
+    <t>Glue Remover</t>
+  </si>
+  <si>
+    <t>წებოს რემუვერი წამწამებისთვის</t>
+  </si>
+  <si>
+    <t>Kirpik Yapışqan Çıxarıcı</t>
+  </si>
+  <si>
+    <t>Кремовый ремувер для снятия ресниц</t>
+  </si>
+  <si>
+    <t>Glue Remover Paste</t>
+  </si>
+  <si>
+    <t>წამწამების წებოს მოსაცილებელი პასტა</t>
+  </si>
+  <si>
+    <t>Kirpik Yapışqan Çıxarıcı Pasta</t>
+  </si>
+  <si>
+    <t>Паста-ремувер для снятия ресниц</t>
+  </si>
+  <si>
+    <t>Cuticle Oil</t>
+  </si>
+  <si>
+    <t>ფრჩხილისა და ნუნების დამატენიანებელი ზეთი</t>
+  </si>
+  <si>
+    <t>Dırnaq və Ətrafı üçün Nəmləndirici Yağ</t>
+  </si>
+  <si>
+    <t>Увлажняющее масло для ногтей и кутикулы</t>
+  </si>
+  <si>
+    <t>Lip Kit</t>
+  </si>
+  <si>
+    <t>USHAS ტუჩის მოვლის ნაკრები</t>
+  </si>
+  <si>
+    <t>USHAS Dodaq Baxım Dəsti</t>
+  </si>
+  <si>
+    <t>Набор для ухода за губами USHAS</t>
+  </si>
+  <si>
+    <t>MICRASTICK</t>
+  </si>
+  <si>
+    <t>წამწამების ფიქსატორი</t>
+  </si>
+  <si>
+    <t>Kirpik Sabitləyici</t>
+  </si>
+  <si>
+    <t>Закрепитель для ресниц</t>
+  </si>
+  <si>
+    <t>მიკრო აპლიკატორები</t>
+  </si>
+  <si>
+    <t>ერთჯერადი მიკრო აპლიკატორები წამწამების დაგრძელებისთვის – 100 ცალი.</t>
+  </si>
+  <si>
+    <t>Kiprik uzadılması üçün birdəfəlik mikro aplikatorlar - 100 ədəd</t>
+  </si>
+  <si>
+    <t>Одноразовые микроаппликаторы для наращивания ресниц – 100 штук.</t>
+  </si>
+  <si>
+    <t>ერთჯერადი ჯაგრისები</t>
+  </si>
+  <si>
+    <t>წამწამების და წარბების ერთჯერადი ჯაგრისები – 50/100 ცალი</t>
+  </si>
+  <si>
+    <t>Kiprik və qaş üçün birdəfəlik fırçalar – 50/100 ədəd</t>
+  </si>
+  <si>
+    <t>Одноразовые щеточки для ресниц и бровей – 50/100 штук</t>
+  </si>
+  <si>
+    <t>აპლიკატორები</t>
+  </si>
+  <si>
+    <t>პროფესიონალური მიკრო-აპლიკატორები (მიკრო-ბრაშები) – 100 ცალი</t>
+  </si>
+  <si>
+    <t>Peşəkar mikro-aplikatorlar (mikro-braşlar) – 100 ədəd</t>
+  </si>
+  <si>
+    <t>Профессиональные микроаппликаторы (микробраши) – 100 штук</t>
+  </si>
+  <si>
+    <t>Microbrushes</t>
+  </si>
+  <si>
+    <t>ერთჯერადი მიკრობრაშები #100</t>
+  </si>
+  <si>
+    <t>Birdəfəlik mikrobraşlar #100</t>
+  </si>
+  <si>
+    <t>Одноразовые микробраши #100</t>
+  </si>
+  <si>
+    <t>Jsy JIESHIYA</t>
+  </si>
+  <si>
+    <t>წამწამების დაგრძელების პროფესიონალური წებო</t>
+  </si>
+  <si>
+    <t>Peşəkar kiprik qaynağı yapışqanı</t>
+  </si>
+  <si>
+    <t>Профессиональный клей для наращивания ресниц</t>
+  </si>
+  <si>
+    <t>NAGARAKU</t>
+  </si>
+  <si>
+    <t>წამწამები NAGARAKU Classic Eyelash (მიქსი)(Mix) წამწამები 7 მმ-დან 15 მმ-მდე.</t>
+  </si>
+  <si>
+    <t>Classic Eyelash kirpikləri (Miks) Paketdə 7 mm-dən 15 mm-ə qədər müxtəlif uzunluqlu (Mix) kirpiklər mövcuddur</t>
+  </si>
+  <si>
+    <t>Ресницы NAGARAKU Classic Eyelash (Микс)</t>
+  </si>
+  <si>
+    <t>წამწამები NAGARAKU Classic Eyelash (მიქსი)(Mix)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classic Eyelash kirpikləri (Miks) </t>
+  </si>
+  <si>
+    <t>LADY BLACK</t>
+  </si>
+  <si>
+    <t>წამწამების დაგრძელების წებო</t>
+  </si>
+  <si>
+    <t>kiprik qaynağı yapışqanı</t>
+  </si>
+  <si>
+    <t>Клей для наращивания ресниц</t>
+  </si>
+  <si>
+    <t>ფრეზები</t>
+  </si>
+  <si>
+    <t>მანიკურის ალმასის საცმები</t>
+  </si>
+  <si>
+    <t>Manikür üçün almaz frezlər</t>
+  </si>
+  <si>
+    <t>Алмазные фрезы для маникюра</t>
+  </si>
+  <si>
+    <t>თავაკების ნაკრები</t>
+  </si>
+  <si>
+    <t>მანიკურის კერამიკული თავაკების ნაკრები</t>
+  </si>
+  <si>
+    <t>Manikür üçün keramik başlıq dəsti</t>
+  </si>
+  <si>
+    <t>Набор керамических фрез для маникюра</t>
+  </si>
+  <si>
+    <t>Diamond Bits Set</t>
+  </si>
+  <si>
+    <t>ალმასის ბურღების ნაკრები</t>
+  </si>
+  <si>
+    <t>Professional almaz başlıq dəsti (6 ədəd)</t>
+  </si>
+  <si>
+    <t>Профессиональный набор алмазных фрез (6 шт).</t>
+  </si>
+  <si>
+    <t>Nail Drill</t>
+  </si>
+  <si>
+    <t>პროფესიონალური მანიკურისა და პედიკურის აპარატი</t>
+  </si>
+  <si>
+    <t>Professional manikür və pedikür aparatı</t>
+  </si>
+  <si>
+    <t>Профессиональный аппарат для маникюра и педикюра</t>
   </si>
 </sst>
 </file>
@@ -1717,15 +1975,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="3" width="40.44140625" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
     <col min="4" max="4" width="6.5546875" customWidth="1"/>
     <col min="5" max="5" width="6.77734375" customWidth="1"/>
-    <col min="6" max="6" width="53.6640625" customWidth="1"/>
+    <col min="6" max="6" width="42.109375" customWidth="1"/>
     <col min="7" max="7" width="47.109375" customWidth="1"/>
     <col min="8" max="9" width="27.44140625" customWidth="1"/>
   </cols>
@@ -2927,14 +3185,576 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="3"/>
-      <c r="B47" s="1"/>
-      <c r="E47" s="6"/>
+      <c r="A47" s="3">
+        <v>10141</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" t="s">
+        <v>180</v>
+      </c>
+      <c r="D47" s="6">
+        <v>18</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" t="s">
+        <v>181</v>
+      </c>
+      <c r="G47" t="s">
+        <v>182</v>
+      </c>
+      <c r="H47" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="48" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="3"/>
-      <c r="B48" s="1"/>
-      <c r="E48" s="6"/>
+      <c r="A48" s="3">
+        <v>10142</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>184</v>
+      </c>
+      <c r="D48" s="6">
+        <v>3</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" t="s">
+        <v>185</v>
+      </c>
+      <c r="G48" t="s">
+        <v>186</v>
+      </c>
+      <c r="H48" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="3">
+        <v>10143</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" t="s">
+        <v>188</v>
+      </c>
+      <c r="D49" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" t="s">
+        <v>189</v>
+      </c>
+      <c r="G49" t="s">
+        <v>190</v>
+      </c>
+      <c r="H49" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="3">
+        <v>10144</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" t="s">
+        <v>192</v>
+      </c>
+      <c r="D50" s="6">
+        <v>13</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" t="s">
+        <v>193</v>
+      </c>
+      <c r="G50" t="s">
+        <v>194</v>
+      </c>
+      <c r="H50" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="3">
+        <v>10145</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>196</v>
+      </c>
+      <c r="D51" s="6">
+        <v>30</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" t="s">
+        <v>197</v>
+      </c>
+      <c r="G51" t="s">
+        <v>198</v>
+      </c>
+      <c r="H51" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="3">
+        <v>10146</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>200</v>
+      </c>
+      <c r="D52" s="6">
+        <v>13</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" t="s">
+        <v>201</v>
+      </c>
+      <c r="G52" t="s">
+        <v>202</v>
+      </c>
+      <c r="H52" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="3">
+        <v>10147</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>204</v>
+      </c>
+      <c r="D53" s="6">
+        <v>19</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" t="s">
+        <v>205</v>
+      </c>
+      <c r="G53" t="s">
+        <v>206</v>
+      </c>
+      <c r="H53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="3">
+        <v>10148</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>208</v>
+      </c>
+      <c r="D54" s="6">
+        <v>10</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" t="s">
+        <v>209</v>
+      </c>
+      <c r="G54" t="s">
+        <v>210</v>
+      </c>
+      <c r="H54" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="3">
+        <v>10149</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" t="s">
+        <v>212</v>
+      </c>
+      <c r="D55" s="6">
+        <v>13</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" t="s">
+        <v>213</v>
+      </c>
+      <c r="G55" t="s">
+        <v>214</v>
+      </c>
+      <c r="H55" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="3">
+        <v>10150</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" t="s">
+        <v>216</v>
+      </c>
+      <c r="D56" s="6">
+        <v>8</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56" t="s">
+        <v>217</v>
+      </c>
+      <c r="G56" t="s">
+        <v>218</v>
+      </c>
+      <c r="H56" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="3">
+        <v>10151</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" t="s">
+        <v>220</v>
+      </c>
+      <c r="D57" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" t="s">
+        <v>221</v>
+      </c>
+      <c r="G57" t="s">
+        <v>222</v>
+      </c>
+      <c r="H57" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="3">
+        <v>10152</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" t="s">
+        <v>224</v>
+      </c>
+      <c r="D58" s="6">
+        <v>8</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F58" t="s">
+        <v>225</v>
+      </c>
+      <c r="G58" t="s">
+        <v>226</v>
+      </c>
+      <c r="H58" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="3">
+        <v>10153</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" t="s">
+        <v>228</v>
+      </c>
+      <c r="D59" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" t="s">
+        <v>229</v>
+      </c>
+      <c r="G59" t="s">
+        <v>230</v>
+      </c>
+      <c r="H59" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="3">
+        <v>10154</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>232</v>
+      </c>
+      <c r="D60" s="6">
+        <v>5</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" t="s">
+        <v>233</v>
+      </c>
+      <c r="G60" t="s">
+        <v>234</v>
+      </c>
+      <c r="H60" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="3">
+        <v>10155</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" t="s">
+        <v>236</v>
+      </c>
+      <c r="D61" s="6">
+        <v>43</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" t="s">
+        <v>237</v>
+      </c>
+      <c r="G61" t="s">
+        <v>238</v>
+      </c>
+      <c r="H61" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="3">
+        <v>10156</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" t="s">
+        <v>240</v>
+      </c>
+      <c r="D62" s="6">
+        <v>15</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" t="s">
+        <v>244</v>
+      </c>
+      <c r="G62" t="s">
+        <v>245</v>
+      </c>
+      <c r="H62" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="3">
+        <v>10157</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>240</v>
+      </c>
+      <c r="D63" s="6">
+        <v>12</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" t="s">
+        <v>241</v>
+      </c>
+      <c r="G63" t="s">
+        <v>242</v>
+      </c>
+      <c r="H63" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="3">
+        <v>10158</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" t="s">
+        <v>246</v>
+      </c>
+      <c r="D64" s="6">
+        <v>45</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64" t="s">
+        <v>247</v>
+      </c>
+      <c r="G64" t="s">
+        <v>248</v>
+      </c>
+      <c r="H64" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="3">
+        <v>10159</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>250</v>
+      </c>
+      <c r="D65" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" t="s">
+        <v>251</v>
+      </c>
+      <c r="G65" t="s">
+        <v>252</v>
+      </c>
+      <c r="H65" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="3">
+        <v>10160</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>254</v>
+      </c>
+      <c r="D66" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F66" t="s">
+        <v>255</v>
+      </c>
+      <c r="G66" t="s">
+        <v>256</v>
+      </c>
+      <c r="H66" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="3">
+        <v>10161</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>258</v>
+      </c>
+      <c r="D67" s="6">
+        <v>10</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F67" t="s">
+        <v>259</v>
+      </c>
+      <c r="G67" t="s">
+        <v>260</v>
+      </c>
+      <c r="H67" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="3">
+        <v>10162</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>262</v>
+      </c>
+      <c r="D68" s="6">
+        <v>90</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F68" t="s">
+        <v>263</v>
+      </c>
+      <c r="G68" t="s">
+        <v>264</v>
+      </c>
+      <c r="H68" t="s">
+        <v>265</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
